--- a/data/trans_orig/P04B3_3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023</t>
+          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>298596</t>
+          <t>300313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>309181</t>
+          <t>309331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>276714</t>
+          <t>277384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>285608</t>
+          <t>285670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>581856</t>
+          <t>580819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593957</t>
+          <t>593051</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40327</t>
+          <t>41794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>84101</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31093</t>
+          <t>31443</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79625</t>
+          <t>79284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126421</t>
+          <t>126470</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428648</t>
+          <t>425573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>471918</t>
+          <t>471186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>452497</t>
+          <t>452243</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>477017</t>
+          <t>476340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>890548</t>
+          <t>890352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>939642</t>
+          <t>940807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,82 +1657,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8450</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>11483</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>6046</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>20114</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8593</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>11483</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>19556</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28221</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49966</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275615</t>
+          <t>278343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297115</t>
+          <t>297399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,82 +1883,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>325149</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>315806</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>331583</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>614006</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>600868</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>626411</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>90,47%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>94,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>325149</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>315835</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>332193</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>614006</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>599542</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>625425</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36385</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61859</t>
+          <t>60885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>268778</t>
+          <t>269216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>295230</t>
+          <t>295264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>434754</t>
+          <t>433427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>460883</t>
+          <t>460400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>714068</t>
+          <t>713928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>752141</t>
+          <t>751440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173626</t>
+          <t>173410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178117</t>
+          <t>178088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>242323</t>
+          <t>241705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254749</t>
+          <t>254343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418191</t>
+          <t>418313</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431195</t>
+          <t>430916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31063</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27806</t>
+          <t>27614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46283</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>229790</t>
+          <t>227876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>247668</t>
+          <t>246697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>227882</t>
+          <t>229167</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>241817</t>
+          <t>242046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>462993</t>
+          <t>464590</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>486778</t>
+          <t>485815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32228</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64276</t>
+          <t>64294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>544000</t>
+          <t>560220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,17 +3644,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>278663</t>
+          <t>278664</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>79989</t>
+          <t>80150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>757081</t>
+          <t>719320</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>581688</t>
+          <t>582083</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>603528</t>
+          <t>604028</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>297041</t>
+          <t>282344</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>763953</t>
+          <t>764545</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>704308</t>
+          <t>734408</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1364747</t>
+          <t>1366478</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>52063</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>151184</t>
+          <t>150525</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>105260</t>
+          <t>103920</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>138422</t>
+          <t>138232</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>136752</t>
+          <t>148432</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>275350</t>
+          <t>276219</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>757132</t>
+          <t>756693</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>876291</t>
+          <t>883444</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>564406</t>
+          <t>564499</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>604156</t>
+          <t>602758</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1336414</t>
+          <t>1337503</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1489984</t>
+          <t>1483696</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>73256</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>74477</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>83956</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>132048</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>199841</t>
+          <t>196839</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>293535</t>
+          <t>290678</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>290415</t>
+          <t>286061</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1168481</t>
+          <t>1100430</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>531560</t>
+          <t>533205</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1493205</t>
+          <t>1399155</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3107973</t>
+          <t>3110816</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3219287</t>
+          <t>3222062</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2494813</t>
+          <t>2564264</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3364277</t>
+          <t>3366754</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5594783</t>
+          <t>5702669</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6533290</t>
+          <t>6531483</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Provincia-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>18376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>306345</t>
+          <t>308104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300313</t>
+          <t>300469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>309331</t>
+          <t>313106</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>282346</t>
+          <t>308325</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277384</t>
+          <t>303230</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>285670</t>
+          <t>311602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>588690</t>
+          <t>616429</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>580819</t>
+          <t>607718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593051</t>
+          <t>622872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>56235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84101</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41611</t>
+          <t>42706</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>99423</t>
+          <t>98941</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79284</t>
+          <t>78603</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126470</t>
+          <t>123087</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>453166</t>
+          <t>467760</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>425573</t>
+          <t>445314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>471186</t>
+          <t>484216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>465422</t>
+          <t>494611</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>452243</t>
+          <t>481021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>476340</t>
+          <t>505626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>918588</t>
+          <t>962371</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>890352</t>
+          <t>937312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>940807</t>
+          <t>985635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>513658</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513658</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513658</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1032048</t>
+          <t>1075841</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1032048</t>
+          <t>1075841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1032048</t>
+          <t>1075841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19694</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50714</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>288858</t>
+          <t>286389</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278343</t>
+          <t>274023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297399</t>
+          <t>295311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>325149</t>
+          <t>328251</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315806</t>
+          <t>318112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331583</t>
+          <t>336297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>614006</t>
+          <t>614641</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>600868</t>
+          <t>600666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>626411</t>
+          <t>627641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>664173</t>
+          <t>671441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>664173</t>
+          <t>671441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>664173</t>
+          <t>671441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>26250</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>42129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36294</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>54144</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>38998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60885</t>
+          <t>74871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>285383</t>
+          <t>341349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269216</t>
+          <t>323498</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>295264</t>
+          <t>352261</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>449214</t>
+          <t>386447</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>433427</t>
+          <t>371713</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>460400</t>
+          <t>396474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>734596</t>
+          <t>727796</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>713928</t>
+          <t>704889</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>751440</t>
+          <t>743967</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>474944</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>474944</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>474944</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>787500</t>
+          <t>793453</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>787500</t>
+          <t>793453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>787500</t>
+          <t>793453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>18248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>200426</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173410</t>
+          <t>194713</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178088</t>
+          <t>203677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>249398</t>
+          <t>218280</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241705</t>
+          <t>211336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254343</t>
+          <t>222629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>426118</t>
+          <t>418705</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418313</t>
+          <t>410272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>430916</t>
+          <t>424397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45259</t>
+          <t>52969</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>239576</t>
+          <t>237238</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>227876</t>
+          <t>226157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>246697</t>
+          <t>246428</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>235881</t>
+          <t>241033</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>229167</t>
+          <t>233390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>242046</t>
+          <t>247202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>475456</t>
+          <t>478270</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>464590</t>
+          <t>465006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>485815</t>
+          <t>490078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>41808</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>19482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>42695</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>257273</t>
+          <t>65812</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64294</t>
+          <t>51203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>560220</t>
+          <t>82506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>278664</t>
+          <t>94887</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80150</t>
+          <t>75801</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>719320</t>
+          <t>114022</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>594120</t>
+          <t>678465</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>582083</t>
+          <t>663214</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>604028</t>
+          <t>689947</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>575947</t>
+          <t>686337</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>282344</t>
+          <t>667210</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>764545</t>
+          <t>701865</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1170066</t>
+          <t>1364801</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>734408</t>
+          <t>1343886</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1366478</t>
+          <t>1385325</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>718509</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>718509</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>718509</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>848535</t>
+          <t>771311</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>848535</t>
+          <t>771311</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>848535</t>
+          <t>771311</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1472649</t>
+          <t>1489820</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1472649</t>
+          <t>1489820</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1472649</t>
+          <t>1489820</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>52063</t>
+          <t>38023</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>105730</t>
+          <t>122208</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>150525</t>
+          <t>143659</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>120971</t>
+          <t>138995</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>120755</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>138232</t>
+          <t>158754</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>226701</t>
+          <t>261202</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>148432</t>
+          <t>236161</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>276219</t>
+          <t>290339</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>807523</t>
+          <t>657745</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>756693</t>
+          <t>635260</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>883444</t>
+          <t>677563</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>584701</t>
+          <t>683778</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>564499</t>
+          <t>662974</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>602758</t>
+          <t>702902</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1392225</t>
+          <t>1341523</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1337503</t>
+          <t>1311954</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1483696</t>
+          <t>1368125</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>52898</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>58289</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>39343</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>72479</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>119243</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>98452</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>142678</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>254060</t>
+          <t>292218</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>196839</t>
+          <t>258210</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>290678</t>
+          <t>326608</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>487822</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>286061</t>
+          <t>296155</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1100430</t>
+          <t>364719</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>741882</t>
+          <t>620124</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>533205</t>
+          <t>576867</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1399155</t>
+          <t>675168</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3151690</t>
+          <t>3177477</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3110816</t>
+          <t>3135900</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3222062</t>
+          <t>3212229</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3168056</t>
+          <t>3347059</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2564264</t>
+          <t>3309386</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3366754</t>
+          <t>3379735</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6319746</t>
+          <t>6524536</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5702669</t>
+          <t>6465687</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6531483</t>
+          <t>6576337</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
